--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFC46FF-5BC6-49B3-B9B9-3070EC9A7592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D492F7D4-742D-40F1-85AA-BB68DD5DBAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="84">
   <si>
     <t>Name:</t>
   </si>
@@ -279,6 +279,15 @@
   </si>
   <si>
     <t>Figured out what actually broke and fixed board with Sabrina. Replaced falling out wires with headers</t>
+  </si>
+  <si>
+    <t>Check-in 9: Met with tyler to demo beta build</t>
+  </si>
+  <si>
+    <t>Release Candidate</t>
+  </si>
+  <si>
+    <t>Clean up main</t>
   </si>
 </sst>
 </file>
@@ -873,7 +882,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>5.4847222222222216</v>
+        <v>5.0124999999999993</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2159,26 +2168,44 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="7"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17"/>
+      <c r="A64" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C64" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D64" s="17">
+        <v>0.5</v>
+      </c>
       <c r="E64" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F64" s="13"/>
+        <v>8.3333333333333315E-2</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="7"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="17"/>
+      <c r="A65" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C65" s="17">
+        <v>0.55555555555555558</v>
+      </c>
       <c r="D65" s="17"/>
       <c r="E65" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F65" s="13"/>
+        <v>-0.55555555555555558</v>
+      </c>
+      <c r="F65" s="13" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="7"/>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D492F7D4-742D-40F1-85AA-BB68DD5DBAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B925A12B-3EB8-4394-8080-0996C31C10B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -287,7 +287,7 @@
     <t>Release Candidate</t>
   </si>
   <si>
-    <t>Clean up main</t>
+    <t>Help Nick merge database into main</t>
   </si>
 </sst>
 </file>
@@ -882,7 +882,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>5.0124999999999993</v>
+        <v>5.1097222222222216</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2190,18 +2190,18 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>82</v>
       </c>
       <c r="C65" s="17">
-        <v>0.55555555555555558</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D65" s="17"/>
       <c r="E65" s="10">
         <f t="shared" si="0"/>
-        <v>-0.55555555555555558</v>
+        <v>-0.45833333333333331</v>
       </c>
       <c r="F65" s="13" t="s">
         <v>83</v>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B925A12B-3EB8-4394-8080-0996C31C10B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB042D3-EF48-4FDA-9A63-A743C8D293B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -287,7 +287,7 @@
     <t>Release Candidate</t>
   </si>
   <si>
-    <t>Help Nick merge database into main</t>
+    <t>Help Nick merge database into main; Made it so http requests are tried until sent for at least 5 times.</t>
   </si>
 </sst>
 </file>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB042D3-EF48-4FDA-9A63-A743C8D293B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F58720D-5C6F-4B64-92A7-8B0315039A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -287,7 +287,7 @@
     <t>Release Candidate</t>
   </si>
   <si>
-    <t>Help Nick merge database into main; Made it so http requests are tried until sent for at least 5 times.</t>
+    <t>Help Nick merge database into main; Made it so http requests are tried until sent for at least 5 times. Updated project issues.</t>
   </si>
 </sst>
 </file>
@@ -882,7 +882,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>5.1097222222222216</v>
+        <v>5.6458333333333321</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2198,10 +2198,12 @@
       <c r="C65" s="17">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D65" s="17"/>
+      <c r="D65" s="17">
+        <v>0.53611111111111109</v>
+      </c>
       <c r="E65" s="10">
         <f t="shared" si="0"/>
-        <v>-0.45833333333333331</v>
+        <v>7.7777777777777779E-2</v>
       </c>
       <c r="F65" s="13" t="s">
         <v>83</v>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F58720D-5C6F-4B64-92A7-8B0315039A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01A13B7-6659-4870-B573-E7B66DC4DF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="86">
   <si>
     <t>Name:</t>
   </si>
@@ -288,6 +288,12 @@
   </si>
   <si>
     <t>Help Nick merge database into main; Made it so http requests are tried until sent for at least 5 times. Updated project issues.</t>
+  </si>
+  <si>
+    <t>Finished integrating fixed NPK code into main</t>
+  </si>
+  <si>
+    <t>Discussed what nneeded to be done and assigned tasks regarding NPK and PCB; Talked through 3D and decided on what structures to go through with; set up documentation and delegated when and who needed to complete what</t>
   </si>
 </sst>
 </file>
@@ -882,7 +888,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>5.6458333333333321</v>
+        <v>5.0708333333333329</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2210,26 +2216,44 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="7"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
+      <c r="A66" s="7">
+        <v>46091</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C66" s="17">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="D66" s="17">
+        <v>0.56111111111111112</v>
+      </c>
       <c r="E66" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F66" s="13"/>
+        <v>0.1166666666666667</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="7"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="17"/>
+      <c r="A67" s="7">
+        <v>46091</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C67" s="17">
+        <v>0.69166666666666665</v>
+      </c>
       <c r="D67" s="17"/>
       <c r="E67" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F67" s="13"/>
+        <v>-0.69166666666666665</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01A13B7-6659-4870-B573-E7B66DC4DF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8932211-C4B0-41A7-B1D0-268CEB05F5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="87">
   <si>
     <t>Name:</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>Discussed what nneeded to be done and assigned tasks regarding NPK and PCB; Talked through 3D and decided on what structures to go through with; set up documentation and delegated when and who needed to complete what</t>
+  </si>
+  <si>
+    <t>Started integrating fixed NPK code into main</t>
   </si>
 </sst>
 </file>
@@ -888,7 +891,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>5.0708333333333329</v>
+        <v>5.8666666666666663</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2246,25 +2249,37 @@
       <c r="C67" s="17">
         <v>0.69166666666666665</v>
       </c>
-      <c r="D67" s="17"/>
+      <c r="D67" s="17">
+        <v>0.70972222222222225</v>
+      </c>
       <c r="E67" s="10">
         <f t="shared" si="0"/>
-        <v>-0.69166666666666665</v>
+        <v>1.8055555555555602E-2</v>
       </c>
       <c r="F67" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="7">
+        <v>46091</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C68" s="17">
+        <v>0.83472222222222225</v>
+      </c>
+      <c r="D68" s="17">
+        <v>0.92083333333333328</v>
+      </c>
+      <c r="E68" s="10">
+        <f t="shared" si="0"/>
+        <v>8.6111111111111027E-2</v>
+      </c>
+      <c r="F68" s="13" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="7"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F68" s="13"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="7"/>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8932211-C4B0-41A7-B1D0-268CEB05F5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571C2E69-5314-41D6-9E56-2CBB4E5F5FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="90">
   <si>
     <t>Name:</t>
   </si>
@@ -281,9 +281,6 @@
     <t>Figured out what actually broke and fixed board with Sabrina. Replaced falling out wires with headers</t>
   </si>
   <si>
-    <t>Check-in 9: Met with tyler to demo beta build</t>
-  </si>
-  <si>
     <t>Release Candidate</t>
   </si>
   <si>
@@ -293,10 +290,22 @@
     <t>Finished integrating fixed NPK code into main</t>
   </si>
   <si>
-    <t>Discussed what nneeded to be done and assigned tasks regarding NPK and PCB; Talked through 3D and decided on what structures to go through with; set up documentation and delegated when and who needed to complete what</t>
-  </si>
-  <si>
     <t>Started integrating fixed NPK code into main</t>
+  </si>
+  <si>
+    <t>Met up with group and instructor to demonstrate and discuss current plans for the permenant housing/hardware for the project.</t>
+  </si>
+  <si>
+    <t>Check-in 9: Met with Tyler to demo beta build</t>
+  </si>
+  <si>
+    <t>Discussed what needed to be done and assigned tasks regarding NPK and PCB; Talked through 3D and decided on what structures to go through with; set up documentation and delegated when and who needed to complete what</t>
+  </si>
+  <si>
+    <t>Check-in 9: Met with tyler to show integration of current databse changes into main, communication error handling, NPK integration, the current arrival and soldering of the new PCB, and the plans for the 3D printed housing.</t>
+  </si>
+  <si>
+    <t>Tested NPK sensor and confirmed it worked with integrated main code. Then proceeded to complete Beta Tests notes.</t>
   </si>
 </sst>
 </file>
@@ -891,7 +900,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>5.8666666666666663</v>
+        <v>5.9493055555555552</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2194,7 +2203,7 @@
         <v>8.3333333333333315E-2</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2202,7 +2211,7 @@
         <v>46084</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C65" s="17">
         <v>0.45833333333333331</v>
@@ -2215,7 +2224,7 @@
         <v>7.7777777777777779E-2</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2223,7 +2232,7 @@
         <v>46091</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C66" s="17">
         <v>0.44444444444444442</v>
@@ -2236,7 +2245,7 @@
         <v>0.1166666666666667</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2244,7 +2253,7 @@
         <v>46091</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C67" s="17">
         <v>0.69166666666666665</v>
@@ -2257,7 +2266,7 @@
         <v>1.8055555555555602E-2</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2265,7 +2274,7 @@
         <v>46091</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C68" s="17">
         <v>0.83472222222222225</v>
@@ -2278,41 +2287,71 @@
         <v>8.6111111111111027E-2</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="7"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
+      <c r="A69" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C69" s="17">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="D69" s="17">
+        <v>0.5</v>
+      </c>
       <c r="E69" s="10">
         <f t="shared" ref="E69:E132" si="1">D69-C69</f>
-        <v>0</v>
-      </c>
-      <c r="F69" s="13"/>
+        <v>1.3888888888888895E-2</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="7"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="17"/>
-      <c r="D70" s="17"/>
+      <c r="A70" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C70" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="D70" s="17">
+        <v>0.51388888888888884</v>
+      </c>
       <c r="E70" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F70" s="13"/>
+        <v>1.388888888888884E-2</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="7"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
+      <c r="A71" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" s="17">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="D71" s="17">
+        <v>0.56874999999999998</v>
+      </c>
       <c r="E71" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F71" s="13"/>
+        <v>5.4861111111111138E-2</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="7"/>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571C2E69-5314-41D6-9E56-2CBB4E5F5FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDF59EA-DDD8-46AA-9D5F-38D6F1E9D774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="91">
   <si>
     <t>Name:</t>
   </si>
@@ -302,10 +302,13 @@
     <t>Discussed what needed to be done and assigned tasks regarding NPK and PCB; Talked through 3D and decided on what structures to go through with; set up documentation and delegated when and who needed to complete what</t>
   </si>
   <si>
-    <t>Check-in 9: Met with tyler to show integration of current databse changes into main, communication error handling, NPK integration, the current arrival and soldering of the new PCB, and the plans for the 3D printed housing.</t>
-  </si>
-  <si>
     <t>Tested NPK sensor and confirmed it worked with integrated main code. Then proceeded to complete Beta Tests notes.</t>
+  </si>
+  <si>
+    <t>Worked on onshape design</t>
+  </si>
+  <si>
+    <t>Check-in 9: Met with tyler to show integration of current database changes into main, communication error handling, NPK integration, the current arrival and soldering of the new PCB, and the plans for the 3D printed housing.</t>
   </si>
 </sst>
 </file>
@@ -900,7 +903,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>5.9493055555555552</v>
+        <v>6.2270833333333329</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2329,7 +2332,7 @@
         <v>1.388888888888884E-2</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2350,30 +2353,50 @@
         <v>5.4861111111111138E-2</v>
       </c>
       <c r="F71" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="7">
+        <v>46094</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C72" s="17">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="D72" s="17">
+        <v>0.90625</v>
+      </c>
+      <c r="E72" s="10">
+        <f t="shared" si="1"/>
+        <v>0.12152777777777779</v>
+      </c>
+      <c r="F72" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="7"/>
-      <c r="B72" s="8"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F72" s="13"/>
-    </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="7"/>
-      <c r="B73" s="8"/>
-      <c r="C73" s="17"/>
-      <c r="D73" s="17"/>
+      <c r="A73" s="7">
+        <v>46095</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="D73" s="17">
+        <v>0.65625</v>
+      </c>
       <c r="E73" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F73" s="13"/>
+        <v>0.15625</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="7"/>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDF59EA-DDD8-46AA-9D5F-38D6F1E9D774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363EA75B-AC6A-4491-80C5-862C44E824CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="93">
   <si>
     <t>Name:</t>
   </si>
@@ -309,6 +309,12 @@
   </si>
   <si>
     <t>Check-in 9: Met with tyler to show integration of current database changes into main, communication error handling, NPK integration, the current arrival and soldering of the new PCB, and the plans for the 3D printed housing.</t>
+  </si>
+  <si>
+    <t>Soldered header pins on newly arrived PCB</t>
+  </si>
+  <si>
+    <t>Brought in new PCB's and components; Discussed what should be done for the 3D CAD, work left to be done, and future meetings</t>
   </si>
 </sst>
 </file>
@@ -903,7 +909,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>6.2270833333333329</v>
+        <v>6.4743055555555538</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2399,48 +2405,88 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="7"/>
-      <c r="B74" s="8"/>
-      <c r="C74" s="17"/>
-      <c r="D74" s="17"/>
+      <c r="A74" s="7">
+        <v>46105</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74" s="17">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="D74" s="17">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="E74" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F74" s="13"/>
+        <v>4.8611111111111049E-2</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="7"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="17"/>
+      <c r="A75" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" s="17">
+        <v>0.41319444444444442</v>
+      </c>
+      <c r="D75" s="17">
+        <v>0.47638888888888886</v>
+      </c>
       <c r="E75" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F75" s="13"/>
+        <v>6.3194444444444442E-2</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="7"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="17"/>
+      <c r="A76" s="7">
+        <v>46106</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="D76" s="17">
+        <v>0.67013888888888884</v>
+      </c>
       <c r="E76" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F76" s="13"/>
+        <v>4.513888888888884E-2</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="7"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
+      <c r="A77" s="7">
+        <v>46107</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" s="17">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="D77" s="17">
+        <v>0.53472222222222221</v>
+      </c>
       <c r="E77" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F77" s="13"/>
+        <v>9.027777777777779E-2</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="7"/>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363EA75B-AC6A-4491-80C5-862C44E824CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCB0A2F-77DB-4CCA-B33F-9A4E63EBA79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="94">
   <si>
     <t>Name:</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>Brought in new PCB's and components; Discussed what should be done for the 3D CAD, work left to be done, and future meetings</t>
+  </si>
+  <si>
+    <t>Fixing onshape design</t>
   </si>
 </sst>
 </file>
@@ -909,7 +912,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>6.4743055555555538</v>
+        <v>6.0263888888888868</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2489,15 +2492,23 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="7"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="17"/>
+      <c r="A78" s="7">
+        <v>46109</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C78" s="17">
+        <v>0.44791666666666669</v>
+      </c>
       <c r="D78" s="17"/>
       <c r="E78" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F78" s="13"/>
+        <v>-0.44791666666666669</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="7"/>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCB0A2F-77DB-4CCA-B33F-9A4E63EBA79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6B6D9E-E5C9-4598-AE4A-6DADE72B05D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -912,7 +912,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>6.0263888888888868</v>
+        <v>6.6805555555555536</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2501,10 +2501,12 @@
       <c r="C78" s="17">
         <v>0.44791666666666669</v>
       </c>
-      <c r="D78" s="17"/>
+      <c r="D78" s="17">
+        <v>0.65416666666666667</v>
+      </c>
       <c r="E78" s="10">
         <f t="shared" si="1"/>
-        <v>-0.44791666666666669</v>
+        <v>0.20624999999999999</v>
       </c>
       <c r="F78" s="13" t="s">
         <v>93</v>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6B6D9E-E5C9-4598-AE4A-6DADE72B05D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F124C94-9E74-4943-8A54-B7236E18E6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="95">
   <si>
     <t>Name:</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>Fixing onshape design</t>
+  </si>
+  <si>
+    <t>Helped merge and fix inconsistied encountered with new handshake protocols and app.</t>
   </si>
 </sst>
 </file>
@@ -912,7 +915,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>6.6805555555555536</v>
+        <v>6.2361111111111089</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2513,15 +2516,23 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="7"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="17"/>
+      <c r="A79" s="7">
+        <v>46112</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79" s="17">
+        <v>0.44444444444444442</v>
+      </c>
       <c r="D79" s="17"/>
       <c r="E79" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F79" s="13"/>
+        <v>-0.44444444444444442</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="7"/>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F124C94-9E74-4943-8A54-B7236E18E6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834B134F-6F73-4E80-9B1E-AD4DD8898AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -320,7 +320,7 @@
     <t>Fixing onshape design</t>
   </si>
   <si>
-    <t>Helped merge and fix inconsistied encountered with new handshake protocols and app.</t>
+    <t>Helped merge and fix inconsistied encountered with new handshake protocols and app., test PCB, adjusted 3D model to fit printer</t>
   </si>
 </sst>
 </file>
@@ -915,7 +915,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>6.2361111111111089</v>
+        <v>6.8979166666666645</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2525,10 +2525,12 @@
       <c r="C79" s="17">
         <v>0.44444444444444442</v>
       </c>
-      <c r="D79" s="17"/>
+      <c r="D79" s="17">
+        <v>0.66180555555555554</v>
+      </c>
       <c r="E79" s="10">
         <f t="shared" si="1"/>
-        <v>-0.44444444444444442</v>
+        <v>0.21736111111111112</v>
       </c>
       <c r="F79" s="13" t="s">
         <v>94</v>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834B134F-6F73-4E80-9B1E-AD4DD8898AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4C1079-1D8D-4671-B6D9-D43E38487ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="97">
   <si>
     <t>Name:</t>
   </si>
@@ -321,6 +321,12 @@
   </si>
   <si>
     <t>Helped merge and fix inconsistied encountered with new handshake protocols and app., test PCB, adjusted 3D model to fit printer</t>
+  </si>
+  <si>
+    <t>Had indstructor meeting at 12; Began integrating final build for TA demo, helped drill holes in water containers, threaded pipes through, soldered new PCB</t>
+  </si>
+  <si>
+    <t>Release Candidate/Instructor Meeting</t>
   </si>
 </sst>
 </file>
@@ -915,7 +921,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>6.8979166666666645</v>
+        <v>7.1784722222222204</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2537,15 +2543,25 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="7"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
+      <c r="A80" s="7">
+        <v>46114</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C80" s="17">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="D80" s="17">
+        <v>0.67986111111111114</v>
+      </c>
       <c r="E80" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F80" s="13"/>
+        <v>0.28055555555555556</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="7"/>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4C1079-1D8D-4671-B6D9-D43E38487ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D395E7-1027-4CE8-8285-1278E1897B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="98">
   <si>
     <t>Name:</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>Release Candidate/Instructor Meeting</t>
+  </si>
+  <si>
+    <t>Check-in 10: Met with Tyler to show integration of current NPK changes, app changes and the PCB</t>
   </si>
 </sst>
 </file>
@@ -921,7 +924,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>7.1784722222222204</v>
+        <v>7.216666666666665</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2337,7 +2340,7 @@
         <v>46093</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="C70" s="17">
         <v>0.5</v>
@@ -2564,15 +2567,25 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="7"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
+      <c r="A81" s="7">
+        <v>46115</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="17">
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="D81" s="17">
+        <v>0.47916666666666669</v>
+      </c>
       <c r="E81" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F81" s="13"/>
+        <v>3.8194444444444475E-2</v>
+      </c>
+      <c r="F81" s="13" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D395E7-1027-4CE8-8285-1278E1897B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52B9851-45A0-40F4-BA42-72B717D24828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="100">
   <si>
     <t>Name:</t>
   </si>
@@ -330,6 +330,12 @@
   </si>
   <si>
     <t>Check-in 10: Met with Tyler to show integration of current NPK changes, app changes and the PCB</t>
+  </si>
+  <si>
+    <t>Production Release</t>
+  </si>
+  <si>
+    <t>Modify added task changes to remove bugs</t>
   </si>
 </sst>
 </file>
@@ -905,7 +911,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" customWidth="1"/>
     <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.21875" bestFit="1" customWidth="1"/>
@@ -924,7 +930,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>7.216666666666665</v>
+        <v>7.2437499999999986</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2588,15 +2594,25 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="7"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
+      <c r="A82" s="7">
+        <v>46126</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C82" s="17">
+        <v>0.44166666666666665</v>
+      </c>
+      <c r="D82" s="17">
+        <v>0.46875</v>
+      </c>
       <c r="E82" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F82" s="13"/>
+        <v>2.7083333333333348E-2</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="7"/>

--- a/Documentation/Contributions/TimeReport_AspenBoler.xlsx
+++ b/Documentation/Contributions/TimeReport_AspenBoler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19042\Downloads\HW\CEN4908\plant-partner\Documentation\Contributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52B9851-45A0-40F4-BA42-72B717D24828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAD87CF-E6FA-43F3-B89A-B27D93FA3D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{605B5A91-C2DF-4ED5-9E2C-366EB894E8F1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="101">
   <si>
     <t>Name:</t>
   </si>
@@ -336,6 +336,9 @@
   </si>
   <si>
     <t>Modify added task changes to remove bugs</t>
+  </si>
+  <si>
+    <t>Tested and adjusted Fernando's code with app and database. Discusses what was left that needs to be completed.</t>
   </si>
 </sst>
 </file>
@@ -930,7 +933,7 @@
       </c>
       <c r="E1" s="6">
         <f>SUM(E4:E199)</f>
-        <v>7.2437499999999986</v>
+        <v>7.3430555555555541</v>
       </c>
       <c r="F1" s="15"/>
     </row>
@@ -2615,15 +2618,25 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="7"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17"/>
+      <c r="A83" s="7">
+        <v>46126</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C83" s="17">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D83" s="17">
+        <v>0.64097222222222228</v>
+      </c>
       <c r="E83" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F83" s="13"/>
+        <v>9.9305555555555647E-2</v>
+      </c>
+      <c r="F83" s="13" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
